--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:37</t>
+    <t xml:space="preserve">2026-09-09 22:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:22</t>
+    <t xml:space="preserve">2026-09-12 19:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:39</t>
+    <t xml:space="preserve">2026-09-24 00:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:17</t>
+    <t xml:space="preserve">2026-09-27 22:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:06</t>
+    <t xml:space="preserve">2026-09-29 11:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -580,7 +580,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>22.25</v>
+        <v>222.46</v>
       </c>
     </row>
     <row r="3">
@@ -597,7 +597,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>20.58</v>
+        <v>205.76</v>
       </c>
     </row>
     <row r="4">
@@ -614,7 +614,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>20.54</v>
+        <v>205.39</v>
       </c>
     </row>
     <row r="5">
@@ -631,7 +631,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>20.47</v>
+        <v>204.65</v>
       </c>
     </row>
     <row r="6">
@@ -648,7 +648,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>19.8</v>
+        <v>198.02</v>
       </c>
     </row>
     <row r="7">
@@ -665,7 +665,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>19.64</v>
+        <v>196.45</v>
       </c>
     </row>
     <row r="8">
@@ -682,7 +682,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>19.18</v>
+        <v>191.81</v>
       </c>
     </row>
     <row r="9">
@@ -699,7 +699,7 @@
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>18.36</v>
+        <v>183.64</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>17.76</v>
+        <v>177.6</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>17.09</v>
+        <v>170.91</v>
       </c>
     </row>
     <row r="12">
@@ -750,7 +750,7 @@
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>16.87</v>
+        <v>168.72</v>
       </c>
     </row>
     <row r="13">
@@ -767,7 +767,7 @@
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>16.57</v>
+        <v>165.72</v>
       </c>
     </row>
     <row r="14">
@@ -784,7 +784,7 @@
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>16.15</v>
+        <v>161.46</v>
       </c>
     </row>
     <row r="15">
@@ -801,7 +801,7 @@
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16.07</v>
+        <v>160.68</v>
       </c>
     </row>
     <row r="16">
@@ -818,7 +818,7 @@
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>16.06</v>
+        <v>160.58</v>
       </c>
     </row>
     <row r="17">
@@ -835,7 +835,7 @@
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>15.55</v>
+        <v>155.5</v>
       </c>
     </row>
     <row r="18">
@@ -852,7 +852,7 @@
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>15.27</v>
+        <v>152.72</v>
       </c>
     </row>
     <row r="19">
@@ -869,7 +869,7 @@
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>15.23</v>
+        <v>152.34</v>
       </c>
     </row>
     <row r="20">
@@ -886,7 +886,7 @@
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>14.91</v>
+        <v>149.08</v>
       </c>
     </row>
     <row r="21">
@@ -903,7 +903,7 @@
         <v>2021</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>14.79</v>
+        <v>147.9</v>
       </c>
     </row>
     <row r="22">
@@ -920,7 +920,7 @@
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>14.75</v>
+        <v>147.52</v>
       </c>
     </row>
     <row r="23">
@@ -937,7 +937,7 @@
         <v>2021</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>14.3</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24">
@@ -954,7 +954,7 @@
         <v>2021</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>13.82</v>
+        <v>138.21</v>
       </c>
     </row>
     <row r="25">
@@ -971,7 +971,7 @@
         <v>2021</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>13.74</v>
+        <v>137.35</v>
       </c>
     </row>
     <row r="26">
@@ -988,7 +988,7 @@
         <v>2021</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>13.42</v>
+        <v>134.23</v>
       </c>
     </row>
     <row r="27">
@@ -1005,7 +1005,7 @@
         <v>2021</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>13.41</v>
+        <v>134.07</v>
       </c>
     </row>
     <row r="28">
@@ -1022,7 +1022,7 @@
         <v>2021</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>13.09</v>
+        <v>130.85</v>
       </c>
     </row>
     <row r="29">
@@ -1039,7 +1039,7 @@
         <v>2021</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>12.83</v>
+        <v>128.26</v>
       </c>
     </row>
     <row r="30">
@@ -1056,7 +1056,7 @@
         <v>2021</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>12.63</v>
+        <v>126.29</v>
       </c>
     </row>
     <row r="31">
@@ -1073,7 +1073,7 @@
         <v>2021</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>12.54</v>
+        <v>125.38</v>
       </c>
     </row>
     <row r="32">
@@ -1090,7 +1090,7 @@
         <v>2021</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>12.26</v>
+        <v>122.6</v>
       </c>
     </row>
     <row r="33">
@@ -1107,7 +1107,7 @@
         <v>2021</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>11.91</v>
+        <v>119.08</v>
       </c>
     </row>
     <row r="34">
@@ -1124,7 +1124,7 @@
         <v>2021</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>11.28</v>
+        <v>112.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:00</t>
+    <t xml:space="preserve">2026-10-01 19:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -162,7 +162,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:25</t>
+    <t xml:space="preserve">2026-10-02 13:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:06</t>
+    <t xml:space="preserve">2026-10-04 07:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 07:56</t>
+    <t xml:space="preserve">2026-10-05 07:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
